--- a/uat-test-plans-reduced30/G2-16144-country-language-location-selector.xlsx
+++ b/uat-test-plans-reduced30/G2-16144-country-language-location-selector.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~30% — 7/10 checks retained, lowest-priority sections dropped] 3 UI-testable stories (G2-17736, G2-17738, G2-19617) with 10 checklist checks covering 12 AC points across country selection, language selection, search, suggested country and footer display.</t>
+          <t>[Reduced V2 ~30% — 7/10 checks retained; AC and core-case coverage guardrails enforced] 3 UI-testable stories (G2-17736, G2-17738, G2-19617) with 10 checklist checks covering 12 AC points across country selection, language selection, search, suggested country and footer display.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=14969; payload_chars=14904; est_tokens~3726; checklist_rows=7; matrix_rows=10; exploratory_rows=5</t>
+          <t>payload_bytes=15654; payload_chars=15587; est_tokens~3897; checklist_rows=7; matrix_rows=11; exploratory_rows=5</t>
         </is>
       </c>
     </row>
@@ -884,10 +884,10 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
     </row>
-    <row r="5" ht="64" customHeight="1">
+    <row r="5" ht="94" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-005</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -897,52 +897,15 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Language Selection</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Changing language on a multi-language country updates the site language</t>
+          <t>Country search by name returns correct results</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>1. Open the country selector while already on a multi-language country.
-2. Change the selected language.
-3. Confirm the selection.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>The site content and navigation update to reflect the newly selected language.
-The footer updates to show the correct language.</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="94" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>UAT-005</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Sane, Sridevi Mayuresh || LuxExperience</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Country search by name returns correct results</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>1. Open the country selector modal.
 2. Type part of a country name in the search field (e.g.
@@ -950,19 +913,54 @@
 4. Verify matching countries appear in the list.</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Matching countries appear in the list as the user types.
 Selecting a result from the list switches the site to that country.</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>UAT-007</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Sane, Sridevi Mayuresh || LuxExperience</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Suggested Country</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Currently selected country appears as the first option in the top section of the modal</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the country selector modal.
+2. Verify that the top section of the modal shows the currently active country as the first listed option.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>The currently active country is shown as the first option in the top section of the country selector modal.</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
     </row>
-    <row r="7" ht="79" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-009</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -972,35 +970,34 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Bag Rectifier</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Country search by ISO code returns the correct country</t>
+          <t>Bag rectifier appears when switching country with items in the bag</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>1. Open the country selector modal.
-2. Type an ISO code in the search field (e.g.
-3. 'DE').
-4. Verify the corresponding country (Germany) appears in the list.</t>
+          <t>1. Add one or more items to the bag.
+2. Open the country selector modal and switch to a different country.
+3. Confirm the selection.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>The correct country matching the ISO code is returned in the search results.
-Selecting the result switches the site to that country.</t>
+          <t>Upon country change with items in bag, the bag rectifier modal or notification appears.
+The customer is informed of any item adjustments due to the country change.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
     </row>
-    <row r="8" ht="64" customHeight="1">
+    <row r="8" ht="79" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UAT-007</t>
+          <t>UAT-010</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1010,23 +1007,23 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Suggested Country</t>
+          <t>Footer Display</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Currently selected country appears as the first option in the top section of the modal</t>
+          <t>Footer displays correct country flag, country name and language/currency after selection</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1. Open the country selector modal.
-2. Verify that the top section of the modal shows the currently active country as the first listed option.</t>
+          <t>1. After changing country and language, check the footer.
+2. Verify the correct country flag, country name, language link (if multi-language) and applied currency are displayed.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>The currently active country is shown as the first option in the top section of the country selector modal.</t>
+          <t>The footer reflects the correct country flag (or no flag for HK, MO, TW if applicable), country name, language selector link and applied currency after any country change.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -1043,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1051,7 +1048,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -1144,7 +1141,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>UAT-002, UAT-003</t>
+          <t>UAT-002, UAT-003, UAT-010</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1201,7 +1198,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>UAT-001, UAT-002, UAT-003, UAT-004</t>
+          <t>UAT-001, UAT-002, UAT-003</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1364,7 +1361,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>UAT-005, UAT-006</t>
+          <t>UAT-005</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1417,7 +1414,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-001, UAT-010</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1470,7 +1467,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>UAT-002, UAT-003</t>
+          <t>UAT-002, UAT-003, UAT-010</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1584,7 +1581,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>UAT-005, UAT-006, UAT-001</t>
+          <t>UAT-005, UAT-001, UAT-010</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1661,6 +1658,63 @@
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="49" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>COV-012</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>G2-16144</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Epic-AC</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Bag rectifier appears on country change with items in bag</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>UAT-009</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>In epic scope ('Show bag rectifier upon country change'); no specific GitHub PR identified for bag rectifier behaviour</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Bag rectifier behaviour during active checkout not explicitly defined — verify with team</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/uat-test-plans-reduced30/G2-16144-country-language-location-selector.xlsx
+++ b/uat-test-plans-reduced30/G2-16144-country-language-location-selector.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~30% — 7/10 checks retained; AC and core-case coverage guardrails enforced] 3 UI-testable stories (G2-17736, G2-17738, G2-19617) with 10 checklist checks covering 12 AC points across country selection, language selection, search, suggested country and footer display.</t>
+          <t>[Reduced V2 ~30% — 7/10 checks retained; AC coverage guardrail enforced] 3 UI-testable stories (G2-17736, G2-17738, G2-19617) with 10 checklist checks covering 12 AC points across country selection, language selection, search, suggested country and footer display.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=15654; payload_chars=15587; est_tokens~3897; checklist_rows=7; matrix_rows=11; exploratory_rows=5</t>
+          <t>payload_bytes=15639; payload_chars=15572; est_tokens~3893; checklist_rows=7; matrix_rows=11; exploratory_rows=5</t>
         </is>
       </c>
     </row>
